--- a/paper/source_data/fig1_source_data.xlsx
+++ b/paper/source_data/fig1_source_data.xlsx
@@ -496,11 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Fig. 1 | BRAN builds one patient state from fragmented retinal, blood and clinical data.**
-**a**, People in the final training fit by source role (circle area proportional to people). Counts, lower bounds rounded down to 20, are not summed because MIMIC-III and MIMIC-IV may share people. A benefit of unpaired single-source training has not been established.
-**b**, Retinal features (384 per photograph), 43 clinical values with masks and typed age form a 192-coordinate state in three 64-coordinate blocks, retinal-associated, shared and clinical-associated, which are not organ-pure. An absent source leaves its block to the learned prior (small states, pale). † Schematic, not participant records.
-**c**, Native heads give 26 recorded conditions (4 of the eye) and 9 blood count values, also from retinal input, and the frozen state gives the red-cell axis and distance from health (Fig. 6). With retina and age alone, MCV and platelet estimates were worse than with age alone (Fig. 2c). Hb, haemoglobin. Hct, haematocrit. RBC and WBC, red and white cell counts. MCV, MCH and MCHC, mean corpuscular volume, haemoglobin and haemoglobin concentration. RDW, red cell distribution width. Plt, platelets.
-**d**, Native linear heads read the posterior mean, auxiliary decoders reconstruct inputs, not pixels, and dots mark each objective's training sources. Dashed readouts are fitted later on the frozen state. Development estimates pool five fold-specific models (1,928 AI-READI participants), and the fold 0 model scores other cohorts. The predecessor model's paired held-out test did not meet its primary end point (Extended Data Fig. 1).</t>
+          <t>**Fig. 1 | BRAN builds one patient state from fragmented retinal, blood and clinical data.** **a**, People in the final training fit by source role (circle area proportional to people). Counts, lower bounds rounded down to 20, are not summed because MIMIC-III and MIMIC-IV may share people. A benefit of unpaired single-source training has not been established. **b**, Retinal features (384 per photograph), 43 clinical values with masks and typed age form a 192-coordinate state in three 64-coordinate blocks, retinal-associated, shared and clinical-associated, which are not organ-pure. An absent source leaves its block to the learned prior (small states, pale). † Schematic, not participant records. **c**, Native heads give 26 self-reported conditions (4 of the eye) and 9 blood count values, also from retinal input, and the frozen state gives the red-cell axis and distance from health (Fig. 6). With retina and age alone, MCV and platelet estimates were worse than with age alone (Fig. 2c). Hb, haemoglobin. Hct, haematocrit. RBC and WBC, red and white cell counts. MCV, MCH and MCHC, mean corpuscular volume, haemoglobin and haemoglobin concentration. RDW, red cell distribution width. Plt, platelets. **d**, Native linear heads read the posterior mean, auxiliary decoders reconstruct inputs, not pixels, and dots mark each objective's training sources. Dashed readouts are fitted later on the frozen state. Development estimates pool five fold-specific models (1,928 AI-READI participants), and the fold 0 model scores other cohorts. The predecessor model's paired held-out test did not meet its primary end point (Extended Data Fig. 1).</t>
         </is>
       </c>
     </row>
